--- a/archive/2026/2026-10-13.xlsx
+++ b/archive/2026/2026-10-13.xlsx
@@ -14,11 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_外資_上櫃" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_投信_上櫃" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_自營商_上櫃" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_外資_上市" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_投信_上市" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_自營商_上市" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_三大法人合計_上市" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2875,3654 +2871,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市自營商買賣超排行｜2026-10-13｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00632R</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>元大台灣50反1</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>69241</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-899486</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00961</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>FT臺灣永續高息</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>34140</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-311509</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>27038</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-187220</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>00918</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>大華優利高填息30</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>14480</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>主動野村台灣50</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-178966</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>12870</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-177385</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>9698</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>00927</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>群益半導體收益</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-134857</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>00664R</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>國泰臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>7638</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-75420</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>00676R</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>富邦臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>5450</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-69779</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>00680L</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>元大美債20正2</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>5383</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-57619</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>00882</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>中信中國高股息</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>5290</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-49531</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>5182</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-37565</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>00646</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>元大S&amp;P500</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>4779</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>00996A</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>主動兆豐台灣豐收</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-31880</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>00686R</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>群益臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>4443</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-30980</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>00994A</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>主動第一金台股優</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>4152</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>00412A</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>主動安聯亞半導體</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-29378</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>00900</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>富邦特選高股息30</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>4147</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-24249</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>00688L</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>國泰20年美債正2</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>4077</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-22626</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>009826</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>貝萊德世界股票</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>3779</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>00947</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>台新臺灣IC設計</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-21537</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>3516</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>00922</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>國泰台灣領袖50</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-17038</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>009820</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>元大納斯達克精選</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>2836</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-16401</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>00939</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>統一台灣高息動能</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>2748</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-14338</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>00713</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>元大台灣高息低波</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>2592</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>台新AI優息動能</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-13609</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2492</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>00712</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>復華富時不動產</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-13266</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>2390</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>00984A</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>主動安聯台灣高息</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-13055</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>00665L</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>富邦恒生國企正2</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>2287</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>00409A</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>主動復華全球50</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-9682</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>2241</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>00673R</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P原油反1</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-9179</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>國喬</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>2218</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-9015</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>2143</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>00934</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>中信成長高股息</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-8065</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>00953B</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>群益優選非投等債</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>2043</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>00878</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>國泰永續高股息</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-7943</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>1996</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>00904</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>台新臺灣半導體30</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-7936</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>1886</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-7894</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>1880</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>00401A</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>主動摩根台灣鑫收</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-7786</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>主動富邦台灣龍耀</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1820</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-7435</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>1583</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-6200</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>00984D</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>主動聯博全球非投</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>1489</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>009803</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>玉山市值動能50</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-6172</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>主動元大AI新經濟</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>1457</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-5646</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>00997A</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>主動群益美國增長</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1456</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>00753L</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>中信中國50正2</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-5424</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>主動安聯台灣</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>1399</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-5043</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>1374</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>006208</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-4404</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>1370</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>00945B</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>凱基美國非投等債</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-3895</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>009813</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>貝萊德標普卓越50</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>1252</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-3687</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>和碩</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>1248</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-3323</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>009805</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>台新美國電力基建</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>1092</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>00912</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>中信臺灣智慧50</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-3086</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>979</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>00663L</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>國泰臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-2602</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>009824</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>群益美國科技巨頭</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>871</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-2580</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>856</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-2396</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>00916</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>國泰全球品牌50</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>829</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>主動群益台灣強棒</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-2308</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>00941</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>中信上游半導體</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>792</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>009821</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>野村稀土關鍵資源</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-2196</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>東聯</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>776</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>00410A</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>主動永豐科技趨勢</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-2133</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>00946</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>群益科技高息成長</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>757</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>00923</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>群益台ESG低碳50</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-1697</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>724</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>00408A</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>主動第一金優股息</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-1525</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市三大法人合計買賣超排行｜2026-10-13｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00632R</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>元大台灣50反1</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>71419</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-1018431</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>61526</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-316196</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>00961</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FT臺灣永續高息</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>41060</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-206800</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>30575</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-199855</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>24389</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-181750</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>23894</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>主動野村台灣50</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-179265</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>23738</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>00927</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>群益半導體收益</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-138168</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>21648</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-136145</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>21144</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-107314</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>國喬</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>21133</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-83561</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>19544</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-64417</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>和碩</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>16969</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-50898</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>00918</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>大華優利高填息30</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>15677</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-49975</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>00953B</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>群益優選非投等債</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>15357</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-47580</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>13274</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-46034</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>12624</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-45353</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>12360</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-41185</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>11936</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-34825</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>10671</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-34654</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>10541</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-33905</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>9688</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>00996A</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>主動兆豐台灣豐收</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-33344</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>9609</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>00412A</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>主動安聯亞半導體</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-29371</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>9586</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-24627</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>9550</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>主動富邦台灣龍耀</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-24617</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>8712</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>00409A</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>主動復華全球50</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-23055</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>中石化</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>8579</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-22477</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>00664R</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>國泰臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>7638</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-22060</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>00984D</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>主動聯博全球非投</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>7504</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>00947</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>台新臺灣IC設計</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-21089</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>東聯</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>7397</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-20144</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>7305</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-19864</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>臺企銀</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>6914</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-18959</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>6736</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-18442</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>東陽</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>6729</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>00922</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>國泰台灣領袖50</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-17016</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>6671</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>主動群益台灣強棒</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-15773</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>富邦金</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>6571</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-14425</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>00900</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>富邦特選高股息30</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>6544</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-14360</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>國票金</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>6516</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>台新AI優息動能</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-13703</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>6106</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-13290</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>6064</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>00984A</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>主動安聯台灣高息</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-13244</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>00676R</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>富邦臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>5616</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-12788</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3706</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>神達</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>5362</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-10608</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>5280</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>00878</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>國泰永續高股息</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-10263</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>00882</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>中信中國高股息</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>5213</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>00401A</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>主動摩根台灣鑫收</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-10158</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>00646</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>元大S&amp;P500</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>4980</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>00673R</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P原油反1</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-9241</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>00680L</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>元大美債20正2</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>4891</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>00904</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>台新臺灣半導體30</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-8531</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2897</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>王道銀行</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>4831</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>00934</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>中信成長高股息</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-7763</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>4782</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-7481</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>00688L</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>國泰20年美債正2</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>4759</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>009803</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>玉山市值動能50</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-6880</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>4740</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-6695</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>和桐</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>4740</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>00753L</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>中信中國50正2</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-6312</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>本檔由程式自動抓取公開網頁整理，僅供參考，不構成投資建議。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>顏色慣例：紅色＝買超／上漲，綠色＝賣超／下跌。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6665,7 +3013,7 @@
         </is>
       </c>
       <c r="K4" s="7" t="n">
-        <v>-5933</v>
+        <v>-5922</v>
       </c>
       <c r="L4" t="n">
         <v>50.9</v>
@@ -6735,7 +3083,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>11713</v>
+        <v>11722</v>
       </c>
       <c r="E6" t="n">
         <v>71.59999999999999</v>
@@ -6781,7 +3129,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>4927</v>
+        <v>4929</v>
       </c>
       <c r="E7" t="n">
         <v>264</v>
@@ -6803,7 +3151,7 @@
         </is>
       </c>
       <c r="K7" s="7" t="n">
-        <v>-3254</v>
+        <v>-3289</v>
       </c>
       <c r="L7" t="n">
         <v>161.5</v>
@@ -6873,7 +3221,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3294</v>
+        <v>3298</v>
       </c>
       <c r="E9" t="n">
         <v>187</v>
@@ -6895,7 +3243,7 @@
         </is>
       </c>
       <c r="K9" s="7" t="n">
-        <v>-1983</v>
+        <v>-2008</v>
       </c>
       <c r="L9" t="n">
         <v>488</v>
@@ -6919,7 +3267,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2999</v>
+        <v>3005</v>
       </c>
       <c r="E10" t="n">
         <v>2490</v>
@@ -6965,7 +3313,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="E11" t="n">
         <v>77.09999999999999</v>
@@ -7033,7 +3381,7 @@
         </is>
       </c>
       <c r="K12" s="7" t="n">
-        <v>-1458</v>
+        <v>-1457</v>
       </c>
       <c r="L12" t="n">
         <v>1775</v>
@@ -7103,7 +3451,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="E14" t="n">
         <v>107.5</v>
@@ -7149,7 +3497,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="E15" t="n">
         <v>740</v>
@@ -7171,7 +3519,7 @@
         </is>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-728</v>
+        <v>-727</v>
       </c>
       <c r="L15" t="n">
         <v>1180</v>
@@ -7241,7 +3589,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="E17" t="n">
         <v>319</v>
@@ -7287,7 +3635,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="E18" t="n">
         <v>148</v>
@@ -7333,7 +3681,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="E19" t="n">
         <v>552</v>
@@ -7355,7 +3703,7 @@
         </is>
       </c>
       <c r="K19" s="7" t="n">
-        <v>-667</v>
+        <v>-665</v>
       </c>
       <c r="L19" t="n">
         <v>508</v>
@@ -7379,7 +3727,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1571</v>
+        <v>1588</v>
       </c>
       <c r="E20" t="n">
         <v>38.75</v>
@@ -7416,22 +3764,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1513</v>
+        <v>1576</v>
       </c>
       <c r="E21" t="n">
-        <v>160</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>1.5</v>
+        <v>141.5</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>-4</v>
       </c>
       <c r="H21" t="n">
         <v>18</v>
@@ -7462,22 +3810,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1508</v>
+        <v>1518</v>
       </c>
       <c r="E22" t="n">
-        <v>103</v>
+        <v>160</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H22" t="n">
         <v>19</v>
@@ -7508,22 +3856,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1493</v>
+        <v>1508</v>
       </c>
       <c r="E23" t="n">
-        <v>141.5</v>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>-4</v>
+        <v>103</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>20</v>
@@ -7554,22 +3902,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>宏致</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1095</v>
+        <v>1303</v>
       </c>
       <c r="E24" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>-0.45</v>
+        <v>183</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="H24" t="n">
         <v>21</v>
@@ -7585,7 +3933,7 @@
         </is>
       </c>
       <c r="K24" s="7" t="n">
-        <v>-423</v>
+        <v>-413</v>
       </c>
       <c r="L24" t="n">
         <v>43</v>
@@ -7600,22 +3948,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>936</v>
+        <v>1098</v>
       </c>
       <c r="E25" t="n">
-        <v>49.35</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>1.7</v>
+        <v>44.75</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>-0.45</v>
       </c>
       <c r="H25" t="n">
         <v>22</v>
@@ -7646,22 +3994,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>901</v>
+        <v>967</v>
       </c>
       <c r="E26" t="n">
-        <v>128</v>
+        <v>1715</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H26" t="n">
         <v>23</v>
@@ -7692,44 +4040,44 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>允強</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>887</v>
+        <v>936</v>
       </c>
       <c r="E27" t="n">
-        <v>23.7</v>
+        <v>49.35</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.15</v>
+        <v>1.7</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="K27" s="7" t="n">
-        <v>-264</v>
+        <v>-269</v>
       </c>
       <c r="L27" t="n">
-        <v>5545</v>
+        <v>950</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>-605</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="28">
@@ -7738,22 +4086,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>超豐</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>881</v>
+        <v>901</v>
       </c>
       <c r="E28" t="n">
-        <v>1440</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
+        <v>128</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>-2</v>
       </c>
       <c r="H28" t="n">
         <v>25</v>
@@ -7784,44 +4132,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>允強</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>783</v>
+        <v>887</v>
       </c>
       <c r="E29" t="n">
-        <v>243.5</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>-8.5</v>
+        <v>23.7</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.15</v>
       </c>
       <c r="H29" t="n">
         <v>26</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="K29" s="7" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="L29" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="M29" s="6" t="n">
-        <v>0.5</v>
+        <v>10060</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>-520</v>
       </c>
     </row>
     <row r="30">
@@ -7830,22 +4178,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>764</v>
+        <v>881</v>
       </c>
       <c r="E30" t="n">
-        <v>240</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>-4.5</v>
+        <v>1440</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>27</v>
@@ -7876,22 +4224,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>744</v>
+        <v>874</v>
       </c>
       <c r="E31" t="n">
-        <v>1170</v>
+        <v>1040</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-65</v>
+        <v>-20</v>
       </c>
       <c r="H31" t="n">
         <v>28</v>
@@ -7922,22 +4270,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>719</v>
+        <v>785</v>
       </c>
       <c r="E32" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
+        <v>243.5</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>-8.5</v>
       </c>
       <c r="H32" t="n">
         <v>29</v>
@@ -7968,22 +4316,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>702</v>
+        <v>765</v>
       </c>
       <c r="E33" t="n">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-8</v>
+        <v>-4.5</v>
       </c>
       <c r="H33" t="n">
         <v>30</v>
@@ -8014,41 +4362,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>695</v>
+        <v>744</v>
       </c>
       <c r="E34" t="n">
-        <v>546</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>17</v>
+        <v>1170</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>-65</v>
       </c>
       <c r="H34" t="n">
         <v>31</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="K34" s="7" t="n">
-        <v>-192</v>
+        <v>-195</v>
       </c>
       <c r="L34" t="n">
-        <v>119</v>
+        <v>46.5</v>
       </c>
       <c r="M34" s="6" t="n">
         <v>0.5</v>
@@ -8060,44 +4408,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>681</v>
+        <v>719</v>
       </c>
       <c r="E35" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>0.8</v>
+        <v>52.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>32</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="K35" s="7" t="n">
-        <v>-182</v>
+        <v>-192</v>
       </c>
       <c r="L35" t="n">
-        <v>10060</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <v>-520</v>
+        <v>119</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -8106,22 +4454,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>655</v>
+        <v>702</v>
       </c>
       <c r="E36" t="n">
-        <v>758</v>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>12</v>
+        <v>279</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>-8</v>
       </c>
       <c r="H36" t="n">
         <v>33</v>
@@ -8152,22 +4500,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>643</v>
+        <v>695</v>
       </c>
       <c r="E37" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>-90</v>
+        <v>546</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>17</v>
       </c>
       <c r="H37" t="n">
         <v>34</v>
@@ -8198,22 +4546,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>639</v>
+        <v>681</v>
       </c>
       <c r="E38" t="n">
-        <v>121.5</v>
+        <v>40.5</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H38" t="n">
         <v>35</v>
@@ -8244,22 +4592,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="E39" t="n">
-        <v>114.5</v>
+        <v>758</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="H39" t="n">
         <v>36</v>
@@ -8290,44 +4638,44 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>593</v>
+        <v>643</v>
       </c>
       <c r="E40" t="n">
-        <v>7275</v>
+        <v>2040</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-50</v>
+        <v>-90</v>
       </c>
       <c r="H40" t="n">
         <v>37</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>彰銀</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="K40" s="7" t="n">
-        <v>-129</v>
+        <v>-169</v>
       </c>
       <c r="L40" t="n">
-        <v>28.45</v>
-      </c>
-      <c r="M40" s="6" t="n">
-        <v>0.2</v>
+        <v>5545</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>-605</v>
       </c>
     </row>
     <row r="41">
@@ -8336,44 +4684,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>588</v>
+        <v>639</v>
       </c>
       <c r="E41" t="n">
-        <v>133</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
+        <v>121.5</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="H41" t="n">
         <v>38</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>彰銀</t>
         </is>
       </c>
       <c r="K41" s="7" t="n">
-        <v>-127</v>
+        <v>-129</v>
       </c>
       <c r="L41" t="n">
-        <v>323</v>
+        <v>28.45</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42">
@@ -8382,44 +4730,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>588</v>
+        <v>637</v>
       </c>
       <c r="E42" t="n">
-        <v>296</v>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>-8.5</v>
+        <v>114.5</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>1.5</v>
       </c>
       <c r="H42" t="n">
         <v>39</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>京鼎</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="K42" s="7" t="n">
-        <v>-122</v>
+        <v>-124</v>
       </c>
       <c r="L42" t="n">
-        <v>283.5</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>-5</v>
+        <v>323</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -8428,44 +4776,44 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>552</v>
+        <v>593</v>
       </c>
       <c r="E43" t="n">
-        <v>1715</v>
+        <v>7275</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-5</v>
+        <v>-50</v>
       </c>
       <c r="H43" t="n">
         <v>40</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>京鼎</t>
         </is>
       </c>
       <c r="K43" s="7" t="n">
-        <v>-105</v>
+        <v>-122</v>
       </c>
       <c r="L43" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="M43" s="6" t="n">
-        <v>1.6</v>
+        <v>283.5</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>-5</v>
       </c>
     </row>
     <row r="44">
@@ -8474,44 +4822,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>541</v>
+        <v>588</v>
       </c>
       <c r="E44" t="n">
-        <v>167</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>-4.5</v>
+        <v>133</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>41</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="K44" s="7" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="L44" t="n">
-        <v>106</v>
+        <v>100.5</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="45">
@@ -8520,44 +4868,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>534</v>
+        <v>588</v>
       </c>
       <c r="E45" t="n">
-        <v>1040</v>
+        <v>296</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-20</v>
+        <v>-8.5</v>
       </c>
       <c r="H45" t="n">
         <v>42</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="K45" s="7" t="n">
-        <v>-96</v>
+        <v>-103</v>
       </c>
       <c r="L45" t="n">
-        <v>116</v>
-      </c>
-      <c r="M45" s="8" t="n">
-        <v>-7</v>
+        <v>106</v>
+      </c>
+      <c r="M45" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -8566,44 +4914,44 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="E46" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>0.4</v>
+        <v>167</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>-4.5</v>
       </c>
       <c r="H46" t="n">
         <v>43</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="K46" s="7" t="n">
-        <v>-83</v>
+        <v>-96</v>
       </c>
       <c r="L46" t="n">
-        <v>2195</v>
+        <v>116</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>-80</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="47">
@@ -8612,44 +4960,44 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>宏致</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="E47" t="n">
-        <v>183</v>
+        <v>27.2</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="H47" t="n">
         <v>44</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>00904</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="K47" s="7" t="n">
+        <v>-83</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2195</v>
+      </c>
+      <c r="M47" s="8" t="n">
         <v>-80</v>
-      </c>
-      <c r="L47" t="n">
-        <v>42.97</v>
-      </c>
-      <c r="M47" s="8" t="n">
-        <v>-1.12</v>
       </c>
     </row>
     <row r="48">
@@ -8680,22 +5028,22 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>00904</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="K48" s="7" t="n">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="L48" t="n">
-        <v>392</v>
+        <v>42.97</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>-26</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="49">
@@ -8726,22 +5074,22 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="K49" s="7" t="n">
-        <v>-59</v>
+        <v>-75</v>
       </c>
       <c r="L49" t="n">
-        <v>43</v>
-      </c>
-      <c r="M49" s="6" t="n">
-        <v>1</v>
+        <v>392</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>-26</v>
       </c>
     </row>
     <row r="50">
@@ -8772,22 +5120,22 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="K50" s="7" t="n">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="L50" t="n">
-        <v>2210</v>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>-60</v>
+        <v>43</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -8805,7 +5153,7 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E51" t="n">
         <v>1175</v>
@@ -8818,22 +5166,22 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="K51" s="7" t="n">
-        <v>-50</v>
+        <v>-58</v>
       </c>
       <c r="L51" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
+        <v>2210</v>
+      </c>
+      <c r="M51" s="8" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="52">
@@ -8864,22 +5212,22 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="K52" s="7" t="n">
-        <v>-45</v>
+        <v>-50</v>
       </c>
       <c r="L52" t="n">
-        <v>966</v>
-      </c>
-      <c r="M52" s="8" t="n">
-        <v>-11</v>
+        <v>67.40000000000001</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -8910,22 +5258,22 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="K53" s="7" t="n">
-        <v>-41</v>
+        <v>-44</v>
       </c>
       <c r="L53" t="n">
-        <v>206</v>
-      </c>
-      <c r="M53" s="6" t="n">
-        <v>0.5</v>
+        <v>966</v>
+      </c>
+      <c r="M53" s="8" t="n">
+        <v>-11</v>
       </c>
     </row>
   </sheetData>
@@ -20141,3613 +16489,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市外資買賣超排行｜2026-10-13｜單位：張</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>本檔由程式自動抓取公開網頁整理，僅供參考，不構成投資建議。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>34488</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-118945</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>22311</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-106150</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>21906</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-97829</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>20171</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-86613</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>19886</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-59673</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>18974</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-46775</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>國喬</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>18915</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-43175</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>16700</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-41446</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>16613</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-37021</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>15863</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>主動富邦台灣龍耀</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-26436</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>和碩</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>15486</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-25641</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>00953B</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>群益優選非投等債</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>13314</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-23001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>13109</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-22470</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>12833</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-19680</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>00712</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>復華富時不動產</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>12641</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-19578</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>10566</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-18900</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>9306</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-17941</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>中石化</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>8879</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-15181</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>7892</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-15042</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>7603</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-14580</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>7392</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>主動群益台灣強棒</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-13465</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>臺企銀</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>7056</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>00409A</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>主動復華全球50</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-13373</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>00961</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>FT臺灣永續高息</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>6920</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-12282</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>6807</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-12199</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>6788</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-11342</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>6787</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-10546</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>東聯</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>6620</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-9080</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>國票金</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>6547</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-8197</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>東陽</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>6496</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-7722</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>6146</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-6797</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>6063</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-6245</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>00984D</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>主動聯博全球非投</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>6015</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>9105</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>泰金寶-DR</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-6010</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>5877</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-5829</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>5852</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>台中銀</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-5549</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>00945B</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>凱基美國非投等債</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>5667</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>啟碁</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-5533</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>3706</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>神達</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>5064</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>主動元大AI新經濟</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-5426</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>富邦金</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>4931</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2312</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>金寶</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-4999</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2897</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>王道銀行</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>4823</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-4962</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>3016</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>嘉晶</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>4513</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-4687</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>和桐</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>4464</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>00994A</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>主動第一金台股優</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-4584</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>00985B</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>群益ESG投等債0-5</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>4206</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>6282</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>康舒</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-4514</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>4189</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>00980A</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>主動野村臺灣優選</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-4371</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>6834</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>天二科技</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>3875</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-4265</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>6209</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>今國光</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>3704</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>全友</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-4255</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>3703</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-3867</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>3312</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-3760</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1409</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>新纖</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>3138</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>晶豪科</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-3678</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>3112</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-3675</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>8039</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>台虹</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>2975</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2399</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>映泰</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-3658</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>亞泥</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>2914</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-3636</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市投信買賣超排行｜2026-10-13｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>15100</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-5922</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>13026</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-5000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>11722</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-4610</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>4929</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-3289</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>4725</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2481</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>強茂</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-2622</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>3298</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-2008</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>3005</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>聯鈞</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-1553</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>2562</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-1500</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>2338</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-1458</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>大成鋼</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>2232</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-1418</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>2032</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>00980A</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>主動野村臺灣優選</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-1127</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1884</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-727</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>1867</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>統一證</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-711</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>1694</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-685</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>1667</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1808</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>潤隆</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-682</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-665</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>1588</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>台灣高鐵</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-647</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>1577</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-470</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>富邦金</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>1518</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2486</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>一詮</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-450</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2637</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>慧洋-KY</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>1508</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-440</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3605</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>宏致</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1303</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-413</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>1098</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-329</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>967</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8112</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>至上</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-294</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>936</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-269</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>超豐</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>901</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>6206</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>飛捷</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-251</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>887</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-213</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>881</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-208</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>874</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4746</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>台耀</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-202</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>785</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>遠東新</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>765</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>9941</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>裕融</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-196</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>744</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-195</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>8070</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>長華*</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>720</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3005</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>神基</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-192</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>矽格</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>702</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-180</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3034</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>聯詠</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>695</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>正新</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-176</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>681</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5534</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>長虹</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-174</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>瑞昱</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>656</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>亞泥</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-173</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>643</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-169</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2615</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>萬海</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>639</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-129</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>637</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-124</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>594</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3413</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>京鼎</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-122</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2458</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>義隆</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>588</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2347</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>聯強</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-105</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>588</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5871</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>中租-KY</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-103</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>日電貿</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>541</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>南茂</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-96</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>534</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-84</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>3014</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>聯陽</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>496</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>00904</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>台新臺灣半導體30</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2451</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>創見</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>496</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>華新科</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-75</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>微星</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>482</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-59</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>472</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-58</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>4961</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>天鈺</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>434</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>9910</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>豐泰</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>技嘉</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>426</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>華碩</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-44</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>顏色慣例：紅色＝買超／上漲，綠色＝賣超／下跌。</t>
+        </is>
       </c>
     </row>
   </sheetData>
